--- a/data/output/evaluasi_18.xlsx
+++ b/data/output/evaluasi_18.xlsx
@@ -8,14 +8,20 @@
   </bookViews>
   <sheets>
     <sheet name="1800" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1804" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1805" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1803" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1808" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="1809" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="1812" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="1872" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="1806" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="1808" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="1810" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="1802" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="1805" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1871" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="1812" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="1804" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="1801" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="1806" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="1807" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="1813" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="1811" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="1872" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,20 +485,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>89.93946331398709</v>
+        <v>17.62187303537446</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25</t>
+          <t>adhb_pi_q2-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -507,20 +513,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>151.1653561195555</v>
+        <v>94.4557108247526</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_pi_q2-25</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -539,7 +545,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30.58967794762421</v>
+        <v>8.651660879373196</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -548,7 +554,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -567,7 +573,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-88.00738218788732</v>
+        <v>-84.60604562899296</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -576,7 +582,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -591,20 +597,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-29.58841839449033</v>
+        <v>-29.70702814597574</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -619,20 +625,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>47.6288781359363</v>
+        <v>-28.59612059042604</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>adhk_pi_q2-25</t>
+          <t>adhk_pi_q1-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -647,20 +653,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>55.23178908289245</v>
+        <v>-31.57748692228644</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25</t>
+          <t>adhk_pi_q2-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -675,20 +681,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-38.10815113038505</v>
+        <v>497.417415759407</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q2-25</t>
+          <t>adhk_pi_q3-25</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -707,16 +713,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.4717154680436574</v>
+        <v>33.2115281030019</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25 vs distribusi_pi_q1-25.1</t>
+          <t>adhk_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -735,16 +741,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.3206993226801557</v>
+        <v>-28.31869096925208</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>distribusi_pi_q2-25 vs distribusi_pi_q2-25.1</t>
+          <t>adhk_net_ekspor_q2-25</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -759,20 +765,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-2.542664376910716</v>
+        <v>-24.91793571690977</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>distribusi_net_ekspor_q1-25 vs distribusi_net_ekspor_q1-25.1</t>
+          <t>adhk_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -787,20 +793,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.063681740705924</v>
+        <v>1.297932095968055</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>distribusi_net_ekspor_q2-25 vs distribusi_net_ekspor_q2-25.1</t>
+          <t>implisit_q-to-q_pklnprt_q1-25 vs implisit_q-to-q_pklnprt_q1-25.1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -819,16 +825,656 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.566848117400843</v>
+        <v>0.9712115702056962</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
+          <t>implisit_q-to-q_pklnprt_q2-25 vs implisit_q-to-q_pklnprt_q2-25.1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>18</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Lampung</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.21893637012101</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q2-25 vs implisit_q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Barat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.008537149595223432</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Barat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-7.890864014340425</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1801</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.154775941373849</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5.195253831253895</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1806</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.124281065034408</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1807</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Way Kanan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.766829813506153</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1807</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Way Kanan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.3700878980228953</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1813</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pesisir Barat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.550823300567471</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1811</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Mesuji</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6781074902595767</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1811</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Mesuji</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.03316540648114472</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1811</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Mesuji</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.147749278382797</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1872</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Metro</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.185420966373456</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -843,7 +1489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -880,11 +1526,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Lampung Timur</t>
+          <t>Kabupaten Lampung Selatan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -893,7 +1539,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40100.6100045983</v>
+        <v>-2121.116912543</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -902,7 +1548,119 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>89265.061713983</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>adhb_pi_q2-25_ril vs adhb_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-26058.379919033</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>63817.712356764</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>adhk_pi_q2-25_ril vs adhk_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1803</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.294227650516083</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -917,7 +1675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -954,253 +1712,141 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1805</v>
+        <v>1808</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Lampung Tengah</t>
+          <t>Kabupaten Tulang Bawang</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-287686.7236661297</v>
+        <v>136317.092263167</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>adhb_pi_q2-25_ril vs adhb_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1805</v>
+        <v>1808</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Lampung Tengah</t>
+          <t>Kabupaten Tulang Bawang</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2034225.471306788</v>
+        <v>-5637.200245826039</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>adhb_net_ekspor_q2-25_ril vs adhb_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1805</v>
+        <v>1808</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Lampung Tengah</t>
+          <t>Kabupaten Tulang Bawang</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-50734.40240800196</v>
+        <v>118484.5418584209</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>adhk_pi_q2-25_ril vs adhk_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1805</v>
+        <v>1808</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Lampung Tengah</t>
+          <t>Kabupaten Tulang Bawang</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1275695.03002521</v>
+        <v>8.760713768741057</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1805</v>
+        <v>1808</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Lampung Tengah</t>
+          <t>Kabupaten Tulang Bawang</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.191955096351116</v>
+        <v>2.282916070176681</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25_ril vs distribusi_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q3-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Distribusi revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1805</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Lampung Tengah</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0.06857836351681196</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1805</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kabupaten Lampung Tengah</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.4555439676760011</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1805</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kabupaten Lampung Tengah</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>-0.2965012233623892</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>sog_q_net_ekspor_q1-25_ril vs sog_q_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1805</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Kabupaten Lampung Tengah</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.8813979512682596</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1265,16 +1911,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>73886.5234960291</v>
+        <v>0.1437039430701156</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -1293,16 +1939,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>64963.13868811098</v>
+        <v>3.088035064431774</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1317,20 +1963,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>55737.86216390043</v>
+        <v>2.476034248612935</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1345,20 +1991,104 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.02003090733178692</v>
+        <v>0.01856017850180742</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pesawaran</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.402914582187949</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pesawaran</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.985681528344834</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1809</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Pesawaran</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.759095567148692</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1373,7 +2103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1410,11 +2140,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1812</v>
+        <v>1802</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Tulang Bawang Barat</t>
+          <t>Kabupaten Tanggamus</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1423,240 +2153,184 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40067.32071740354</v>
+        <v>2.945094437277551</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1812</v>
+        <v>1802</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Tulang Bawang Barat</t>
+          <t>Kabupaten Tanggamus</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-298859.349235428</v>
+        <v>-0.5802853356843728</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1812</v>
+        <v>1802</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Tulang Bawang Barat</t>
+          <t>Kabupaten Tanggamus</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36261.52513189529</v>
+        <v>21.7090804266484</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Angka revisi berlawanan arah</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1812</v>
+        <v>1802</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Tulang Bawang Barat</t>
+          <t>Kabupaten Tanggamus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-84556.861561495</v>
+        <v>19.08584930249397</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1812</v>
+        <v>1802</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Tulang Bawang Barat</t>
+          <t>Kabupaten Tanggamus</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.058070124518735</v>
+        <v>0.3360056835039402</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25_ril vs distribusi_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Distribusi revisi berlawanan arah</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1812</v>
+        <v>1802</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Tulang Bawang Barat</t>
+          <t>Kabupaten Tanggamus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.810898887225344</v>
+        <v>-2.738946417872608</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1812</v>
+        <v>1802</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kabupaten Tulang Bawang Barat</t>
+          <t>Kabupaten Tanggamus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-2.131972939023548</v>
+        <v>-2.515274641535608</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_q_net_ekspor_q1-25_ril vs sog_q_net_ekspor_q1-25_rev</t>
+          <t>sog_q_pi_q3-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1812</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kabupaten Tulang Bawang Barat</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.9975028301440493</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1812</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Kabupaten Tulang Bawang Barat</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>1.350725642964883</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1671,7 +2345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1708,11 +2382,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1872</v>
+        <v>1805</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Metro</t>
+          <t>Kabupaten Lampung Tengah</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1721,100 +2395,72 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6090.83848501091</v>
+        <v>3.932651477290274</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1872</v>
+        <v>1805</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kota Metro</t>
+          <t>Kabupaten Lampung Tengah</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>5626.58250724943</v>
+        <v>2.030122086456936</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1872</v>
+        <v>1805</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kota Metro</t>
+          <t>Kabupaten Lampung Tengah</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8664794264563732</v>
+        <v>-2.255476239575618</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>sog_q_pi_q3-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1872</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kota Metro</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.2464360252950344</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1829,7 +2475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1866,11 +2512,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1806</v>
+        <v>1871</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Lampung Utara</t>
+          <t>Kota Bandar Lampung</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1879,54 +2525,54 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-651918.5980089246</v>
+        <v>5.559496568525442</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1806</v>
+        <v>1871</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Lampung Utara</t>
+          <t>Kota Bandar Lampung</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-6.228422968353912</v>
+        <v>-6.434569751437518</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1806</v>
+        <v>1871</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Lampung Utara</t>
+          <t>Kota Bandar Lampung</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1935,156 +2581,44 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-6.228422968353912</v>
+        <v>4.382465071476557</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1806</v>
+        <v>1871</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Lampung Utara</t>
+          <t>Kota Bandar Lampung</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.519994916399845</v>
+        <v>-2.637871993205185</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1806</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kabupaten Lampung Utara</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>3.506326882195022</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1806</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Kabupaten Lampung Utara</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>4.595872851693003</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1806</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Kabupaten Lampung Utara</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>-0.1607353193929975</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sog_q_net_ekspor_q1-25_ril vs sog_q_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>1806</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Kabupaten Lampung Utara</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>-0.3085886641355895</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -2099,7 +2633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2136,113 +2670,85 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1808</v>
+        <v>1812</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Tulang Bawang</t>
+          <t>Kabupaten Tulang Bawang Barat</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>44172.8233486384</v>
+        <v>6.264734114885782</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1808</v>
+        <v>1812</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Tulang Bawang</t>
+          <t>Kabupaten Tulang Bawang Barat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.1284884832627293</v>
+        <v>4.498606787389583</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1808</v>
+        <v>1812</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Tulang Bawang</t>
+          <t>Kabupaten Tulang Bawang Barat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3745245296383817</v>
+        <v>4.953615638267413</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q3-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>1808</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Kabupaten Tulang Bawang</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>0.06190232836822437</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_net_ekspor_q1-25_ril vs sog_y-on-y_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2294,29 +2800,113 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1810</v>
+        <v>1804</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Pringsewu</t>
+          <t>Kabupaten Lampung Timur</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.001567449271102824</v>
+        <v>-1.849263721343417</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Timur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.882787612608805</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Timur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>10.65508195322559</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1804</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Lampung Timur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2.08483342327535</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
